--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:15</t>
+    <t xml:space="preserve">2026-09-29 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:02</t>
+    <t xml:space="preserve">2026-09-29 18:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,10 +504,10 @@
         <v>15.97</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>54.86</v>
+        <v>54.87</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>38.89</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +518,7 @@
         <v>8.01</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>40.37</v>
+        <v>40.38</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>32.36</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:42</t>
+    <t xml:space="preserve">2026-10-05 04:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -521,7 +521,7 @@
         <v>40.38</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.36</v>
+        <v>32.37</v>
       </c>
     </row>
   </sheetData>
